--- a/Models/Свиньи/results/Свиньи - Лучшие модели.xlsx
+++ b/Models/Свиньи/results/Свиньи - Лучшие модели.xlsx
@@ -462,17 +462,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.04</v>
+        <v>35.99</v>
       </c>
       <c r="C2" t="n">
-        <v>33.15</v>
+        <v>34.23</v>
       </c>
       <c r="D2" t="n">
-        <v>27.95</v>
+        <v>31.66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>Prophet</t>
         </is>
       </c>
     </row>
@@ -483,17 +483,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.31</v>
+        <v>23.21</v>
       </c>
       <c r="C3" t="n">
-        <v>23.86</v>
+        <v>17.36</v>
       </c>
       <c r="D3" t="n">
-        <v>61.17</v>
+        <v>59.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>92.73999999999999</v>
+        <v>193.8</v>
       </c>
       <c r="C4" t="n">
-        <v>115.71</v>
+        <v>196.48</v>
       </c>
       <c r="D4" t="n">
-        <v>191.75</v>
+        <v>308.04</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1.720769583627235e+20</v>
+        <v>1.560150713042329e+20</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
@@ -542,17 +542,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.01</v>
+        <v>27.16</v>
       </c>
       <c r="C6" t="n">
-        <v>29.98</v>
+        <v>34.98</v>
       </c>
       <c r="D6" t="n">
-        <v>28.19</v>
+        <v>19.05</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>Prophet</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>6.541660546981151e+19</v>
+        <v>4.753769302223073e+18</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2.911976557526964e+20</v>
+        <v>1.088086260619153e+20</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56.16</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>9.06</v>
+        <v>38.45</v>
       </c>
       <c r="D9" t="n">
-        <v>42.68</v>
+        <v>58.29</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -618,13 +618,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37.39</v>
+        <v>41.37</v>
       </c>
       <c r="C10" t="n">
-        <v>19.91</v>
+        <v>24.22</v>
       </c>
       <c r="D10" t="n">
-        <v>32.11</v>
+        <v>40.19</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.5</v>
+        <v>11.99</v>
       </c>
       <c r="C11" t="n">
-        <v>13.43</v>
+        <v>11.33</v>
       </c>
       <c r="D11" t="n">
-        <v>14.54</v>
+        <v>13.42</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8.630000000000001</v>
+        <v>15.53</v>
       </c>
       <c r="C12" t="n">
-        <v>10.61</v>
+        <v>16.62</v>
       </c>
       <c r="D12" t="n">
-        <v>7.92</v>
+        <v>15.19</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -681,17 +681,17 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20.99</v>
+        <v>29.3</v>
       </c>
       <c r="C13" t="n">
-        <v>22.32</v>
+        <v>25.73</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01</v>
+        <v>33.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -702,17 +702,17 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>170.24</v>
+        <v>31.71</v>
       </c>
       <c r="C14" t="n">
-        <v>161.48</v>
+        <v>28.63</v>
       </c>
       <c r="D14" t="n">
-        <v>128.32</v>
+        <v>62.14</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>5.941923480432439e+17</v>
+        <v>3.566357919365962e+17</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.66</v>
+        <v>34.83</v>
       </c>
       <c r="C16" t="n">
-        <v>48.1</v>
+        <v>38.66</v>
       </c>
       <c r="D16" t="n">
-        <v>122.67</v>
+        <v>75.97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>49.64</v>
+        <v>58.23</v>
       </c>
       <c r="C17" t="n">
-        <v>55.61</v>
+        <v>168.03</v>
       </c>
       <c r="D17" t="n">
-        <v>113.62</v>
+        <v>226.78</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>8.335332840358918e+22</v>
+        <v>2.304214110064169e+21</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
@@ -799,17 +799,17 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12.78</v>
+        <v>16.26</v>
       </c>
       <c r="C19" t="n">
-        <v>11.24</v>
+        <v>14.41</v>
       </c>
       <c r="D19" t="n">
-        <v>9.15</v>
+        <v>20.42</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -820,13 +820,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28.13</v>
+        <v>24.42</v>
       </c>
       <c r="C20" t="n">
-        <v>21.45</v>
+        <v>16.9</v>
       </c>
       <c r="D20" t="n">
-        <v>62.26</v>
+        <v>43.71</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -840,14 +840,18 @@
           <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>107.47</v>
+      </c>
       <c r="C21" t="n">
-        <v>3.613712429618653e+22</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>71.05</v>
+      </c>
+      <c r="D21" t="n">
+        <v>61.93</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>Prophet</t>
         </is>
       </c>
     </row>
